--- a/A10 - NMR/NMR.xlsx
+++ b/A10 - NMR/NMR.xlsx
@@ -1,22 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonas\Documents\Praktikum-IV\A10 - NMR\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92795A88-41C5-440C-838E-46F6878F02DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="60" windowWidth="10395" windowHeight="7575"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
     <sheet name="List2" sheetId="2" r:id="rId2"/>
     <sheet name="List3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t>Amplituda</t>
   </si>
@@ -41,11 +60,14 @@
   <si>
     <t>T1</t>
   </si>
+  <si>
+    <t>Indukce B0</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -76,8 +98,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
@@ -88,12 +111,15 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="cs-CZ"/>
   <c:roundedCorners val="0"/>
@@ -229,6 +255,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0DFE-4ABB-B3AD-87997061CD45}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -275,7 +306,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
@@ -291,7 +321,7 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="cs-CZ"/>
   <c:roundedCorners val="0"/>
@@ -455,6 +485,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D3A1-4B6B-8743-C90A96852EE3}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -501,7 +536,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
@@ -533,7 +567,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Graf 1"/>
+        <xdr:cNvPr id="2" name="Graf 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -563,7 +603,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Graf 3"/>
+        <xdr:cNvPr id="4" name="Graf 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -582,9 +628,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motiv systému Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Kancelář">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -622,7 +668,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Kancelář">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -694,7 +740,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Kancelář">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -867,22 +913,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E47"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" customWidth="1"/>
-    <col min="4" max="4" width="19.28515625" customWidth="1"/>
+    <col min="1" max="1" width="19.44140625" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -896,7 +942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>40</v>
       </c>
@@ -910,7 +956,7 @@
         <v>3.866E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>38</v>
       </c>
@@ -924,7 +970,7 @@
         <v>4.5399999999999998E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -938,7 +984,7 @@
         <v>8.8299999999999993E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -952,7 +998,7 @@
         <v>1.154E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -966,7 +1012,7 @@
         <v>1.473E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>8</v>
       </c>
@@ -980,7 +1026,7 @@
         <v>2.5319999999999999E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>10</v>
       </c>
@@ -994,7 +1040,7 @@
         <v>2.8379999999999999E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>12</v>
       </c>
@@ -1008,7 +1054,7 @@
         <v>2.6970000000000001E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>14</v>
       </c>
@@ -1022,7 +1068,7 @@
         <v>3.2980000000000002E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>16</v>
       </c>
@@ -1036,7 +1082,7 @@
         <v>3.4889999999999997E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>18</v>
       </c>
@@ -1050,7 +1096,7 @@
         <v>3.5560000000000001E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>20</v>
       </c>
@@ -1064,7 +1110,7 @@
         <v>3.6490000000000002E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>22</v>
       </c>
@@ -1078,7 +1124,7 @@
         <v>3.6630000000000003E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>24</v>
       </c>
@@ -1092,7 +1138,7 @@
         <v>3.7019999999999997E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>26</v>
       </c>
@@ -1106,7 +1152,7 @@
         <v>3.9219999999999998E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>28</v>
       </c>
@@ -1114,7 +1160,7 @@
         <v>1.1860000000000001E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>30</v>
       </c>
@@ -1122,7 +1168,7 @@
         <v>2.9960000000000001E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>32</v>
       </c>
@@ -1130,7 +1176,7 @@
         <v>3.7940000000000002E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>34</v>
       </c>
@@ -1138,7 +1184,7 @@
         <v>2.879E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>36</v>
       </c>
@@ -1146,12 +1192,12 @@
         <v>1.0319999999999999E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -1162,7 +1208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>0.1</v>
       </c>
@@ -1173,7 +1219,7 @@
         <v>5.176E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>0.2</v>
       </c>
@@ -1184,7 +1230,7 @@
         <v>5.3449999999999998E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>0.3</v>
       </c>
@@ -1195,7 +1241,7 @@
         <v>3.798E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>0.4</v>
       </c>
@@ -1206,7 +1252,7 @@
         <v>3.3029999999999997E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>0.51</v>
       </c>
@@ -1214,7 +1260,7 @@
         <v>2.928E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B32">
         <v>0.61</v>
       </c>
@@ -1222,7 +1268,7 @@
         <v>2.63E-2</v>
       </c>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>0.71</v>
       </c>
@@ -1230,7 +1276,7 @@
         <v>2.3179999999999999E-2</v>
       </c>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B34">
         <v>0.81</v>
       </c>
@@ -1238,7 +1284,7 @@
         <v>2.0160000000000001E-2</v>
       </c>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B35">
         <v>0.91</v>
       </c>
@@ -1246,7 +1292,7 @@
         <v>1.8200000000000001E-2</v>
       </c>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B36">
         <v>1.01</v>
       </c>
@@ -1254,7 +1300,7 @@
         <v>1.6150000000000001E-2</v>
       </c>
     </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B37">
         <v>1.1100000000000001</v>
       </c>
@@ -1262,7 +1308,7 @@
         <v>1.456E-2</v>
       </c>
     </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B38">
         <v>1.41</v>
       </c>
@@ -1270,7 +1316,7 @@
         <v>1.042E-2</v>
       </c>
     </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B39">
         <v>2.0099999999999998</v>
       </c>
@@ -1278,7 +1324,7 @@
         <v>5.9899999999999997E-3</v>
       </c>
     </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B40">
         <v>2.5099999999999998</v>
       </c>
@@ -1286,7 +1332,7 @@
         <v>3.82E-3</v>
       </c>
     </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B41">
         <v>3.01</v>
       </c>
@@ -1294,7 +1340,7 @@
         <v>2.2200000000000002E-3</v>
       </c>
     </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B42">
         <v>3.51</v>
       </c>
@@ -1302,7 +1348,7 @@
         <v>1.7899999999999999E-3</v>
       </c>
     </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B43">
         <v>4.01</v>
       </c>
@@ -1310,12 +1356,23 @@
         <v>1.4E-3</v>
       </c>
     </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B44">
         <v>5.01</v>
       </c>
       <c r="C44">
         <v>8.0000000000000004E-4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B46" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B47" s="1">
+        <f>18.307/42.51299</f>
+        <v>0.43062132303561801</v>
       </c>
     </row>
   </sheetData>
@@ -1325,18 +1382,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>

--- a/A10 - NMR/NMR.xlsx
+++ b/A10 - NMR/NMR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonas\Documents\Praktikum-IV\A10 - NMR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92795A88-41C5-440C-838E-46F6878F02DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0B99ADB-A4B9-4683-B210-80FE3ED91067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>Amplituda</t>
   </si>
@@ -63,11 +63,17 @@
   <si>
     <t>Indukce B0</t>
   </si>
+  <si>
+    <t>Indukce B1</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="167" formatCode="0.00000"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -98,9 +104,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
@@ -914,7 +921,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.44140625" customWidth="1"/>
@@ -1373,6 +1380,17 @@
       <c r="B47" s="1">
         <f>18.307/42.51299</f>
         <v>0.43062132303561801</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B49" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B50" s="2">
+        <f>0.344/267.11</f>
+        <v>1.2878589345213581E-3</v>
       </c>
     </row>
   </sheetData>

--- a/A10 - NMR/NMR.xlsx
+++ b/A10 - NMR/NMR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonas\Documents\Praktikum-IV\A10 - NMR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0B99ADB-A4B9-4683-B210-80FE3ED91067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1251D14-3F41-494B-988B-58888209EA3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -72,7 +72,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="167" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="0.00000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -107,7 +107,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
@@ -1260,6 +1260,9 @@
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>0.5</v>
+      </c>
       <c r="B31">
         <v>0.51</v>
       </c>
@@ -1268,6 +1271,9 @@
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>0.6</v>
+      </c>
       <c r="B32">
         <v>0.61</v>
       </c>
@@ -1275,7 +1281,10 @@
         <v>2.63E-2</v>
       </c>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>0.7</v>
+      </c>
       <c r="B33">
         <v>0.71</v>
       </c>
@@ -1283,7 +1292,10 @@
         <v>2.3179999999999999E-2</v>
       </c>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>0.8</v>
+      </c>
       <c r="B34">
         <v>0.81</v>
       </c>
@@ -1291,7 +1303,10 @@
         <v>2.0160000000000001E-2</v>
       </c>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>0.9</v>
+      </c>
       <c r="B35">
         <v>0.91</v>
       </c>
@@ -1299,7 +1314,10 @@
         <v>1.8200000000000001E-2</v>
       </c>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>1</v>
+      </c>
       <c r="B36">
         <v>1.01</v>
       </c>
@@ -1307,7 +1325,10 @@
         <v>1.6150000000000001E-2</v>
       </c>
     </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="B37">
         <v>1.1100000000000001</v>
       </c>
@@ -1315,7 +1336,10 @@
         <v>1.456E-2</v>
       </c>
     </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>1.4</v>
+      </c>
       <c r="B38">
         <v>1.41</v>
       </c>
@@ -1323,7 +1347,10 @@
         <v>1.042E-2</v>
       </c>
     </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>2</v>
+      </c>
       <c r="B39">
         <v>2.0099999999999998</v>
       </c>
@@ -1331,7 +1358,10 @@
         <v>5.9899999999999997E-3</v>
       </c>
     </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>2.5</v>
+      </c>
       <c r="B40">
         <v>2.5099999999999998</v>
       </c>
@@ -1339,7 +1369,10 @@
         <v>3.82E-3</v>
       </c>
     </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>3</v>
+      </c>
       <c r="B41">
         <v>3.01</v>
       </c>
@@ -1347,7 +1380,10 @@
         <v>2.2200000000000002E-3</v>
       </c>
     </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>3.5</v>
+      </c>
       <c r="B42">
         <v>3.51</v>
       </c>
@@ -1355,7 +1391,10 @@
         <v>1.7899999999999999E-3</v>
       </c>
     </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>4</v>
+      </c>
       <c r="B43">
         <v>4.01</v>
       </c>
@@ -1363,7 +1402,10 @@
         <v>1.4E-3</v>
       </c>
     </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>5</v>
+      </c>
       <c r="B44">
         <v>5.01</v>
       </c>
@@ -1371,12 +1413,12 @@
         <v>8.0000000000000004E-4</v>
       </c>
     </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B47" s="1">
         <f>18.307/42.51299</f>
         <v>0.43062132303561801</v>

--- a/A10 - NMR/NMR.xlsx
+++ b/A10 - NMR/NMR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonas\Documents\Praktikum-IV\A10 - NMR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1251D14-3F41-494B-988B-58888209EA3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8710763-F914-41E4-9643-23EA35696F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <si>
     <t>Amplituda</t>
   </si>
@@ -65,6 +65,18 @@
   </si>
   <si>
     <t>Indukce B1</t>
+  </si>
+  <si>
+    <t>Šum</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>1/sqrt(N)</t>
+  </si>
+  <si>
+    <t>stdev</t>
   </si>
 </sst>
 </file>
@@ -104,10 +116,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
@@ -921,7 +934,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.44140625" customWidth="1"/>
@@ -1424,15 +1437,127 @@
         <v>0.43062132303561801</v>
       </c>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B50" s="2">
         <f>0.344/267.11</f>
         <v>1.2878589345213581E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>11</v>
+      </c>
+      <c r="B53" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>2</v>
+      </c>
+      <c r="B54">
+        <f>1/SQRT(A54)</f>
+        <v>0.70710678118654746</v>
+      </c>
+      <c r="C54" s="3">
+        <v>2.1742500000000001E-4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>4</v>
+      </c>
+      <c r="B55">
+        <f t="shared" ref="B55:B61" si="0">1/SQRT(A55)</f>
+        <v>0.5</v>
+      </c>
+      <c r="C55" s="3">
+        <v>1.45935E-4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>8</v>
+      </c>
+      <c r="B56">
+        <f t="shared" si="0"/>
+        <v>0.35355339059327373</v>
+      </c>
+      <c r="C56" s="3">
+        <v>1.06135E-4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>16</v>
+      </c>
+      <c r="B57">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+      <c r="C57" s="3">
+        <v>7.2517799999999999E-5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>23</v>
+      </c>
+      <c r="B58">
+        <f t="shared" si="0"/>
+        <v>0.20851441405707477</v>
+      </c>
+      <c r="C58" s="3">
+        <v>6.2044000000000004E-5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>64</v>
+      </c>
+      <c r="B59">
+        <f t="shared" si="0"/>
+        <v>0.125</v>
+      </c>
+      <c r="C59" s="3">
+        <v>3.9325E-5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>128</v>
+      </c>
+      <c r="B60">
+        <f t="shared" si="0"/>
+        <v>8.8388347648318433E-2</v>
+      </c>
+      <c r="C60" s="3">
+        <v>2.75322E-5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>256</v>
+      </c>
+      <c r="B61">
+        <f t="shared" si="0"/>
+        <v>6.25E-2</v>
+      </c>
+      <c r="C61" s="3">
+        <v>1.8377599999999998E-5</v>
       </c>
     </row>
   </sheetData>
